--- a/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -201,12 +201,103 @@
   </si>
   <si>
     <t>Thu Jul 09 22:56:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:04:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:05:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:07:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:07:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:08:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:08:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:09:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:09:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:10:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:10:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:11:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:13:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:13:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:14:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:15:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:15:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:16:44 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -573,12 +664,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.59765625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="49.1328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="40.86328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1328125" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.59765625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.86328125" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -603,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -620,7 +711,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -637,7 +728,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -654,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -671,7 +762,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -688,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -705,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -722,7 +813,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -739,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -756,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -773,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -790,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -807,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -824,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -841,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -858,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -875,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -892,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -909,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -926,7 +1017,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -943,7 +1034,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -960,7 +1051,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -977,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -994,7 +1085,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1011,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1028,7 +1119,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1045,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1062,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1079,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1096,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINmoreThan9Error.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -201,12 +201,103 @@
   </si>
   <si>
     <t>Thu Jul 09 22:56:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:06:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:07:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:08:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:08:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:08:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:08:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:08:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:09:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:13 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -573,12 +664,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.59765625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="49.1328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="40.86328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1328125" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.59765625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.86328125" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -603,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -620,7 +711,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -637,7 +728,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -654,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -671,7 +762,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -688,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -705,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -722,7 +813,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -739,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -756,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -773,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -790,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -807,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -824,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -841,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -858,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -875,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -892,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -909,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -926,7 +1017,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -943,7 +1034,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -960,7 +1051,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -977,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -994,7 +1085,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1011,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1028,7 +1119,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1045,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1062,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1079,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1096,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
